--- a/data/raw/holdings-daily-us-en-rokt.xlsx
+++ b/data/raw/holdings-daily-us-en-rokt.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="175">
   <si>
     <t>Fund Name:</t>
   </si>
@@ -192,7 +192,7 @@
     <t>ROKT</t>
   </si>
   <si>
-    <t>As of 28-Aug-2026</t>
+    <t>As of 01-Sep-2026</t>
   </si>
   <si>
     <t>Name</t>
@@ -285,6 +285,30 @@
     <t>2522096</t>
   </si>
   <si>
+    <t>IRIDIUM COMMUNICATIONS INC</t>
+  </si>
+  <si>
+    <t>IRDM</t>
+  </si>
+  <si>
+    <t>46269C102</t>
+  </si>
+  <si>
+    <t>B2QH310</t>
+  </si>
+  <si>
+    <t>TELEDYNE TECHNOLOGIES INC</t>
+  </si>
+  <si>
+    <t>TDY</t>
+  </si>
+  <si>
+    <t>879360105</t>
+  </si>
+  <si>
+    <t>2503477</t>
+  </si>
+  <si>
     <t>HEICO CORP</t>
   </si>
   <si>
@@ -297,18 +321,6 @@
     <t>2419217</t>
   </si>
   <si>
-    <t>TELEDYNE TECHNOLOGIES INC</t>
-  </si>
-  <si>
-    <t>TDY</t>
-  </si>
-  <si>
-    <t>879360105</t>
-  </si>
-  <si>
-    <t>2503477</t>
-  </si>
-  <si>
     <t>HEXCEL CORP</t>
   </si>
   <si>
@@ -321,18 +333,6 @@
     <t>2416779</t>
   </si>
   <si>
-    <t>IRIDIUM COMMUNICATIONS INC</t>
-  </si>
-  <si>
-    <t>IRDM</t>
-  </si>
-  <si>
-    <t>46269C102</t>
-  </si>
-  <si>
-    <t>B2QH310</t>
-  </si>
-  <si>
     <t>BOEING CO/THE</t>
   </si>
   <si>
@@ -393,6 +393,18 @@
     <t>BK9DTN5</t>
   </si>
   <si>
+    <t>LEIDOS HOLDINGS INC</t>
+  </si>
+  <si>
+    <t>LDOS</t>
+  </si>
+  <si>
+    <t>525327102</t>
+  </si>
+  <si>
+    <t>BDV82B8</t>
+  </si>
+  <si>
     <t>VOYAGER TECHNOLOGIES INC A</t>
   </si>
   <si>
@@ -405,16 +417,64 @@
     <t>BQMJ1G9</t>
   </si>
   <si>
-    <t>LEIDOS HOLDINGS INC</t>
-  </si>
-  <si>
-    <t>LDOS</t>
-  </si>
-  <si>
-    <t>525327102</t>
-  </si>
-  <si>
-    <t>BDV82B8</t>
+    <t>TECHNIPFMC PLC</t>
+  </si>
+  <si>
+    <t>FTI</t>
+  </si>
+  <si>
+    <t>G87110105</t>
+  </si>
+  <si>
+    <t>BDSFG98</t>
+  </si>
+  <si>
+    <t>AMPHENOL CORP CL A</t>
+  </si>
+  <si>
+    <t>APH</t>
+  </si>
+  <si>
+    <t>032095101</t>
+  </si>
+  <si>
+    <t>2145084</t>
+  </si>
+  <si>
+    <t>GENERAL DYNAMICS CORP</t>
+  </si>
+  <si>
+    <t>GD</t>
+  </si>
+  <si>
+    <t>369550108</t>
+  </si>
+  <si>
+    <t>2365161</t>
+  </si>
+  <si>
+    <t>KBR INC</t>
+  </si>
+  <si>
+    <t>KBR</t>
+  </si>
+  <si>
+    <t>48242W106</t>
+  </si>
+  <si>
+    <t>B1HHB18</t>
+  </si>
+  <si>
+    <t>VIASAT INC</t>
+  </si>
+  <si>
+    <t>VSAT</t>
+  </si>
+  <si>
+    <t>92552V100</t>
+  </si>
+  <si>
+    <t>2946243</t>
   </si>
   <si>
     <t>SPIRE GLOBAL INC</t>
@@ -429,64 +489,28 @@
     <t>BRC45W5</t>
   </si>
   <si>
-    <t>GENERAL DYNAMICS CORP</t>
-  </si>
-  <si>
-    <t>GD</t>
-  </si>
-  <si>
-    <t>369550108</t>
-  </si>
-  <si>
-    <t>2365161</t>
-  </si>
-  <si>
-    <t>KBR INC</t>
-  </si>
-  <si>
-    <t>KBR</t>
-  </si>
-  <si>
-    <t>48242W106</t>
-  </si>
-  <si>
-    <t>B1HHB18</t>
-  </si>
-  <si>
-    <t>VIASAT INC</t>
-  </si>
-  <si>
-    <t>VSAT</t>
-  </si>
-  <si>
-    <t>92552V100</t>
-  </si>
-  <si>
-    <t>2946243</t>
-  </si>
-  <si>
-    <t>TECHNIPFMC PLC</t>
-  </si>
-  <si>
-    <t>FTI</t>
-  </si>
-  <si>
-    <t>G87110105</t>
-  </si>
-  <si>
-    <t>BDSFG98</t>
-  </si>
-  <si>
-    <t>AMPHENOL CORP CL A</t>
-  </si>
-  <si>
-    <t>APH</t>
-  </si>
-  <si>
-    <t>032095101</t>
-  </si>
-  <si>
-    <t>2145084</t>
+    <t>HUNTINGTON INGALLS INDUSTRIE</t>
+  </si>
+  <si>
+    <t>HII</t>
+  </si>
+  <si>
+    <t>446413106</t>
+  </si>
+  <si>
+    <t>B40SSC9</t>
+  </si>
+  <si>
+    <t>STANDEX INTERNATIONAL CORP</t>
+  </si>
+  <si>
+    <t>SXI</t>
+  </si>
+  <si>
+    <t>854231107</t>
+  </si>
+  <si>
+    <t>2840174</t>
   </si>
   <si>
     <t>REDWIRE CORP</t>
@@ -501,30 +525,6 @@
     <t>BL5FDV8</t>
   </si>
   <si>
-    <t>STANDEX INTERNATIONAL CORP</t>
-  </si>
-  <si>
-    <t>SXI</t>
-  </si>
-  <si>
-    <t>854231107</t>
-  </si>
-  <si>
-    <t>2840174</t>
-  </si>
-  <si>
-    <t>HUNTINGTON INGALLS INDUSTRIE</t>
-  </si>
-  <si>
-    <t>HII</t>
-  </si>
-  <si>
-    <t>446413106</t>
-  </si>
-  <si>
-    <t>B40SSC9</t>
-  </si>
-  <si>
     <t>TRANSDIGM GROUP INC</t>
   </si>
   <si>
@@ -561,6 +561,18 @@
     <t>BM8JV32</t>
   </si>
   <si>
+    <t>BWX TECHNOLOGIES INC</t>
+  </si>
+  <si>
+    <t>BWXT</t>
+  </si>
+  <si>
+    <t>05605H100</t>
+  </si>
+  <si>
+    <t>BZ0W624</t>
+  </si>
+  <si>
     <t>FIREFLY AEROSPACE INC</t>
   </si>
   <si>
@@ -573,6 +585,18 @@
     <t>BPK4SR9</t>
   </si>
   <si>
+    <t>ELBIT SYSTEMS LTD</t>
+  </si>
+  <si>
+    <t>ESLT</t>
+  </si>
+  <si>
+    <t>M3760D101</t>
+  </si>
+  <si>
+    <t>2311614</t>
+  </si>
+  <si>
     <t>ROCKET LAB CORP</t>
   </si>
   <si>
@@ -585,18 +609,6 @@
     <t>BT6C8Z3</t>
   </si>
   <si>
-    <t>ELBIT SYSTEMS LTD</t>
-  </si>
-  <si>
-    <t>ESLT</t>
-  </si>
-  <si>
-    <t>M3760D101</t>
-  </si>
-  <si>
-    <t>2311614</t>
-  </si>
-  <si>
     <t>PARSONS CORP</t>
   </si>
   <si>
@@ -609,18 +621,6 @@
     <t>BJN4N02</t>
   </si>
   <si>
-    <t>BWX TECHNOLOGIES INC</t>
-  </si>
-  <si>
-    <t>BWXT</t>
-  </si>
-  <si>
-    <t>05605H100</t>
-  </si>
-  <si>
-    <t>BZ0W624</t>
-  </si>
-  <si>
     <t>INTUITIVE MACHINES INC</t>
   </si>
   <si>
@@ -673,6 +673,12 @@
   </si>
   <si>
     <t>924QSGII3</t>
+  </si>
+  <si>
+    <t>US DOLLAR</t>
+  </si>
+  <si>
+    <t>999USDZ92</t>
   </si>
 </sst>
 </file>
@@ -774,7 +780,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -828,6 +834,12 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true" applyNumberFormat="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true" applyNumberFormat="true">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true" applyNumberFormat="true">
@@ -1377,7 +1389,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L141"/>
+  <dimension ref="A1:L142"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="31.0"/>
@@ -1455,13 +1467,13 @@
         <v>24</v>
       </c>
       <c r="E6" t="n" s="19">
-        <v>4.225897</v>
+        <v>4.373265</v>
       </c>
       <c r="F6" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G6" t="n" s="20">
-        <v>162841.0</v>
+        <v>159129.0</v>
       </c>
       <c r="H6" t="s" s="18">
         <v>26</v>
@@ -1481,13 +1493,13 @@
         <v>30</v>
       </c>
       <c r="E7" t="n" s="21">
-        <v>4.176139</v>
+        <v>4.346892</v>
       </c>
       <c r="F7" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G7" t="n" s="22">
-        <v>100994.0</v>
+        <v>98690.0</v>
       </c>
       <c r="H7" t="s" s="18">
         <v>26</v>
@@ -1507,13 +1519,13 @@
         <v>34</v>
       </c>
       <c r="E8" t="n" s="23">
-        <v>3.91798</v>
+        <v>3.873099</v>
       </c>
       <c r="F8" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G8" t="n" s="24">
-        <v>36077.0</v>
+        <v>35253.0</v>
       </c>
       <c r="H8" t="s" s="18">
         <v>26</v>
@@ -1533,13 +1545,13 @@
         <v>38</v>
       </c>
       <c r="E9" t="n" s="25">
-        <v>3.772912</v>
+        <v>3.684384</v>
       </c>
       <c r="F9" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G9" t="n" s="26">
-        <v>41719.0</v>
+        <v>40771.0</v>
       </c>
       <c r="H9" t="s" s="18">
         <v>26</v>
@@ -1559,13 +1571,13 @@
         <v>42</v>
       </c>
       <c r="E10" t="n" s="27">
-        <v>3.541419</v>
+        <v>3.489709</v>
       </c>
       <c r="F10" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G10" t="n" s="28">
-        <v>12244.0</v>
+        <v>11968.0</v>
       </c>
       <c r="H10" t="s" s="18">
         <v>26</v>
@@ -1585,13 +1597,13 @@
         <v>46</v>
       </c>
       <c r="E11" t="n" s="29">
-        <v>3.454137</v>
+        <v>3.430977</v>
       </c>
       <c r="F11" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G11" t="n" s="30">
-        <v>20009.0</v>
+        <v>137134.0</v>
       </c>
       <c r="H11" t="s" s="18">
         <v>26</v>
@@ -1611,13 +1623,13 @@
         <v>50</v>
       </c>
       <c r="E12" t="n" s="31">
-        <v>3.404537</v>
+        <v>3.40896</v>
       </c>
       <c r="F12" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G12" t="n" s="32">
-        <v>10671.0</v>
+        <v>10427.0</v>
       </c>
       <c r="H12" t="s" s="18">
         <v>26</v>
@@ -1637,13 +1649,13 @@
         <v>54</v>
       </c>
       <c r="E13" t="n" s="33">
-        <v>3.403018</v>
+        <v>3.404607</v>
       </c>
       <c r="F13" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G13" t="n" s="34">
-        <v>69927.0</v>
+        <v>19553.0</v>
       </c>
       <c r="H13" t="s" s="18">
         <v>26</v>
@@ -1663,13 +1675,13 @@
         <v>58</v>
       </c>
       <c r="E14" t="n" s="35">
-        <v>3.354589</v>
+        <v>3.3696</v>
       </c>
       <c r="F14" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G14" t="n" s="36">
-        <v>140334.0</v>
+        <v>68335.0</v>
       </c>
       <c r="H14" t="s" s="18">
         <v>26</v>
@@ -1689,13 +1701,13 @@
         <v>62</v>
       </c>
       <c r="E15" t="n" s="37">
-        <v>3.308146</v>
+        <v>3.307971</v>
       </c>
       <c r="F15" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G15" t="n" s="38">
-        <v>30736.0</v>
+        <v>30036.0</v>
       </c>
       <c r="H15" t="s" s="18">
         <v>26</v>
@@ -1715,13 +1727,13 @@
         <v>66</v>
       </c>
       <c r="E16" t="n" s="39">
-        <v>3.291019</v>
+        <v>3.294713</v>
       </c>
       <c r="F16" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G16" t="n" s="40">
-        <v>11813.0</v>
+        <v>11545.0</v>
       </c>
       <c r="H16" t="s" s="18">
         <v>26</v>
@@ -1741,13 +1753,13 @@
         <v>70</v>
       </c>
       <c r="E17" t="n" s="41">
-        <v>3.232806</v>
+        <v>3.213857</v>
       </c>
       <c r="F17" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G17" t="n" s="42">
-        <v>16821.0</v>
+        <v>16441.0</v>
       </c>
       <c r="H17" t="s" s="18">
         <v>26</v>
@@ -1767,13 +1779,13 @@
         <v>74</v>
       </c>
       <c r="E18" t="n" s="43">
-        <v>2.994018</v>
+        <v>2.951517</v>
       </c>
       <c r="F18" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G18" t="n" s="44">
-        <v>21074.0</v>
+        <v>20594.0</v>
       </c>
       <c r="H18" t="s" s="18">
         <v>26</v>
@@ -1793,13 +1805,13 @@
         <v>78</v>
       </c>
       <c r="E19" t="n" s="45">
-        <v>2.858957</v>
+        <v>2.925262</v>
       </c>
       <c r="F19" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G19" t="n" s="46">
-        <v>21206.0</v>
+        <v>20726.0</v>
       </c>
       <c r="H19" t="s" s="18">
         <v>26</v>
@@ -1819,13 +1831,13 @@
         <v>82</v>
       </c>
       <c r="E20" t="n" s="47">
-        <v>2.727192</v>
+        <v>2.707026</v>
       </c>
       <c r="F20" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G20" t="n" s="48">
-        <v>155045.0</v>
+        <v>36320.0</v>
       </c>
       <c r="H20" t="s" s="18">
         <v>26</v>
@@ -1845,13 +1857,13 @@
         <v>86</v>
       </c>
       <c r="E21" t="n" s="49">
-        <v>2.681535</v>
+        <v>2.67421</v>
       </c>
       <c r="F21" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G21" t="n" s="50">
-        <v>37164.0</v>
+        <v>151509.0</v>
       </c>
       <c r="H21" t="s" s="18">
         <v>26</v>
@@ -1871,13 +1883,13 @@
         <v>90</v>
       </c>
       <c r="E22" t="n" s="51">
-        <v>2.649675</v>
+        <v>2.63702</v>
       </c>
       <c r="F22" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G22" t="n" s="52">
-        <v>392208.0</v>
+        <v>62882.0</v>
       </c>
       <c r="H22" t="s" s="18">
         <v>26</v>
@@ -1897,13 +1909,13 @@
         <v>94</v>
       </c>
       <c r="E23" t="n" s="53">
-        <v>2.57039</v>
+        <v>2.578643</v>
       </c>
       <c r="F23" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G23" t="n" s="54">
-        <v>13210.0</v>
+        <v>29509.0</v>
       </c>
       <c r="H23" t="s" s="18">
         <v>26</v>
@@ -1923,13 +1935,13 @@
         <v>98</v>
       </c>
       <c r="E24" t="n" s="55">
-        <v>2.567628</v>
+        <v>2.553905</v>
       </c>
       <c r="F24" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G24" t="n" s="56">
-        <v>131618.0</v>
+        <v>12910.0</v>
       </c>
       <c r="H24" t="s" s="18">
         <v>26</v>
@@ -1949,13 +1961,13 @@
         <v>102</v>
       </c>
       <c r="E25" t="n" s="57">
-        <v>2.530075</v>
+        <v>2.545678</v>
       </c>
       <c r="F25" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G25" t="n" s="58">
-        <v>73211.0</v>
+        <v>128618.0</v>
       </c>
       <c r="H25" t="s" s="18">
         <v>26</v>
@@ -1975,13 +1987,13 @@
         <v>106</v>
       </c>
       <c r="E26" t="n" s="59">
-        <v>2.503441</v>
+        <v>2.539332</v>
       </c>
       <c r="F26" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G26" t="n" s="60">
-        <v>64350.0</v>
+        <v>71543.0</v>
       </c>
       <c r="H26" t="s" s="18">
         <v>26</v>
@@ -2001,13 +2013,13 @@
         <v>110</v>
       </c>
       <c r="E27" t="n" s="61">
-        <v>2.443409</v>
+        <v>2.467224</v>
       </c>
       <c r="F27" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G27" t="n" s="62">
-        <v>30197.0</v>
+        <v>383296.0</v>
       </c>
       <c r="H27" t="s" s="18">
         <v>26</v>
@@ -2027,13 +2039,13 @@
         <v>114</v>
       </c>
       <c r="E28" t="n" s="63">
-        <v>2.399873</v>
+        <v>2.393079</v>
       </c>
       <c r="F28" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G28" t="n" s="64">
-        <v>430396.0</v>
+        <v>15282.0</v>
       </c>
       <c r="H28" t="s" s="18">
         <v>26</v>
@@ -2053,13 +2065,13 @@
         <v>118</v>
       </c>
       <c r="E29" t="n" s="65">
-        <v>2.374276</v>
+        <v>2.314252</v>
       </c>
       <c r="F29" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G29" t="n" s="66">
-        <v>15509.0</v>
+        <v>15157.0</v>
       </c>
       <c r="H29" t="s" s="18">
         <v>26</v>
@@ -2079,13 +2091,13 @@
         <v>122</v>
       </c>
       <c r="E30" t="n" s="67">
-        <v>2.360093</v>
+        <v>2.31084</v>
       </c>
       <c r="F30" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G30" t="n" s="68">
-        <v>15638.0</v>
+        <v>420584.0</v>
       </c>
       <c r="H30" t="s" s="18">
         <v>26</v>
@@ -2105,13 +2117,13 @@
         <v>126</v>
       </c>
       <c r="E31" t="n" s="69">
-        <v>2.263726</v>
+        <v>2.251027</v>
       </c>
       <c r="F31" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G31" t="n" s="70">
-        <v>3721.0</v>
+        <v>3637.0</v>
       </c>
       <c r="H31" t="s" s="18">
         <v>26</v>
@@ -2131,13 +2143,13 @@
         <v>130</v>
       </c>
       <c r="E32" t="n" s="71">
-        <v>2.141983</v>
+        <v>2.141887</v>
       </c>
       <c r="F32" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G32" t="n" s="72">
-        <v>11542.0</v>
+        <v>11282.0</v>
       </c>
       <c r="H32" t="s" s="18">
         <v>26</v>
@@ -2157,13 +2169,13 @@
         <v>134</v>
       </c>
       <c r="E33" t="n" s="73">
-        <v>2.135319</v>
+        <v>2.099863</v>
       </c>
       <c r="F33" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G33" t="n" s="74">
-        <v>208342.0</v>
+        <v>203594.0</v>
       </c>
       <c r="H33" t="s" s="18">
         <v>26</v>
@@ -2183,13 +2195,13 @@
         <v>138</v>
       </c>
       <c r="E34" t="n" s="75">
-        <v>2.088311</v>
+        <v>2.081525</v>
       </c>
       <c r="F34" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G34" t="n" s="76">
-        <v>191488.0</v>
+        <v>24062.0</v>
       </c>
       <c r="H34" t="s" s="18">
         <v>26</v>
@@ -2209,13 +2221,13 @@
         <v>142</v>
       </c>
       <c r="E35" t="n" s="77">
-        <v>2.012784</v>
+        <v>2.071285</v>
       </c>
       <c r="F35" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G35" t="n" s="78">
-        <v>60938.0</v>
+        <v>187124.0</v>
       </c>
       <c r="H35" t="s" s="18">
         <v>26</v>
@@ -2235,13 +2247,13 @@
         <v>146</v>
       </c>
       <c r="E36" t="n" s="79">
-        <v>2.010686</v>
+        <v>2.052053</v>
       </c>
       <c r="F36" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G36" t="n" s="80">
-        <v>5531.0</v>
+        <v>5407.0</v>
       </c>
       <c r="H36" t="s" s="18">
         <v>26</v>
@@ -2261,13 +2273,13 @@
         <v>150</v>
       </c>
       <c r="E37" t="n" s="81">
-        <v>2.004702</v>
+        <v>1.994387</v>
       </c>
       <c r="F37" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G37" t="n" s="82">
-        <v>79756.0</v>
+        <v>59550.0</v>
       </c>
       <c r="H37" t="s" s="18">
         <v>26</v>
@@ -2287,13 +2299,13 @@
         <v>154</v>
       </c>
       <c r="E38" t="n" s="83">
-        <v>1.930542</v>
+        <v>1.935285</v>
       </c>
       <c r="F38" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G38" t="n" s="84">
-        <v>24622.0</v>
+        <v>77936.0</v>
       </c>
       <c r="H38" t="s" s="18">
         <v>26</v>
@@ -2313,13 +2325,13 @@
         <v>158</v>
       </c>
       <c r="E39" t="n" s="85">
-        <v>1.90169</v>
+        <v>1.857956</v>
       </c>
       <c r="F39" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G39" t="n" s="86">
-        <v>241199.0</v>
+        <v>235699.0</v>
       </c>
       <c r="H39" t="s" s="18">
         <v>26</v>
@@ -2339,13 +2351,13 @@
         <v>162</v>
       </c>
       <c r="E40" t="n" s="87">
-        <v>1.737487</v>
+        <v>1.711668</v>
       </c>
       <c r="F40" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G40" t="n" s="88">
-        <v>15578.0</v>
+        <v>15222.0</v>
       </c>
       <c r="H40" t="s" s="18">
         <v>26</v>
@@ -2365,13 +2377,13 @@
         <v>166</v>
       </c>
       <c r="E41" t="n" s="89">
-        <v>1.597611</v>
+        <v>1.584347</v>
       </c>
       <c r="F41" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G41" t="n" s="90">
-        <v>26249.0</v>
+        <v>25653.0</v>
       </c>
       <c r="H41" t="s" s="18">
         <v>26</v>
@@ -2391,13 +2403,13 @@
         <v>170</v>
       </c>
       <c r="E42" t="n" s="91">
-        <v>1.297502</v>
+        <v>1.257299</v>
       </c>
       <c r="F42" t="s" s="18">
         <v>25</v>
       </c>
       <c r="G42" t="n" s="92">
-        <v>15578.0</v>
+        <v>15222.0</v>
       </c>
       <c r="H42" t="s" s="18">
         <v>26</v>
@@ -2417,7 +2429,7 @@
         <v>25</v>
       </c>
       <c r="E43" t="n" s="93">
-        <v>0.119802</v>
+        <v>0.125067</v>
       </c>
       <c r="F43" t="s" s="18">
         <v>25</v>
@@ -2429,37 +2441,50 @@
         <v>26</v>
       </c>
     </row>
-    <row r="44"/>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A46" s="12" t="s">
+    <row r="44">
+      <c r="A44" t="s" s="18">
+        <v>173</v>
+      </c>
+      <c r="B44" t="s" s="18">
+        <v>25</v>
+      </c>
+      <c r="C44" t="s" s="18">
+        <v>174</v>
+      </c>
+      <c r="D44" t="s" s="18">
+        <v>25</v>
+      </c>
+      <c r="E44" t="n" s="95">
+        <v>-3.0E-5</v>
+      </c>
+      <c r="F44" t="s" s="18">
+        <v>25</v>
+      </c>
+      <c r="G44" t="n" s="96">
+        <v>-55.25</v>
+      </c>
+      <c r="H44" t="s" s="18">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="45"/>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A47" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B46" s="12"/>
-      <c r="C46" s="12"/>
-      <c r="D46" s="12"/>
-      <c r="E46" s="12"/>
-      <c r="F46" s="12"/>
-      <c r="G46" s="12"/>
-      <c r="H46" s="12"/>
-      <c r="I46" s="12"/>
-    </row>
-    <row r="48" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="14" t="s">
+      <c r="B47" s="12"/>
+      <c r="C47" s="12"/>
+      <c r="D47" s="12"/>
+      <c r="E47" s="12"/>
+      <c r="F47" s="12"/>
+      <c r="G47" s="12"/>
+      <c r="H47" s="12"/>
+      <c r="I47" s="12"/>
+    </row>
+    <row r="49" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="14"/>
-      <c r="J48" s="1"/>
-      <c r="K48" s="1"/>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A49" s="14"/>
       <c r="B49" s="14"/>
       <c r="C49" s="14"/>
       <c r="D49" s="14"/>
@@ -2485,36 +2510,35 @@
       <c r="K50" s="1"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A51" s="10"/>
-      <c r="B51" s="10"/>
-      <c r="C51" s="10"/>
-      <c r="D51" s="10"/>
-      <c r="E51" s="10"/>
-      <c r="F51" s="10"/>
-      <c r="G51" s="10"/>
-      <c r="H51" s="10"/>
-      <c r="I51" s="10"/>
+      <c r="A51" s="14"/>
+      <c r="B51" s="14"/>
+      <c r="C51" s="14"/>
+      <c r="D51" s="14"/>
+      <c r="E51" s="14"/>
+      <c r="F51" s="14"/>
+      <c r="G51" s="14"/>
+      <c r="H51" s="14"/>
+      <c r="I51" s="14"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
     </row>
-    <row r="52" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="13" t="s">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A52" s="10"/>
+      <c r="B52" s="10"/>
+      <c r="C52" s="10"/>
+      <c r="D52" s="10"/>
+      <c r="E52" s="10"/>
+      <c r="F52" s="10"/>
+      <c r="G52" s="10"/>
+      <c r="H52" s="10"/>
+      <c r="I52" s="10"/>
+      <c r="J52" s="1"/>
+      <c r="K52" s="1"/>
+    </row>
+    <row r="53" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B52" s="13"/>
-      <c r="C52" s="13"/>
-      <c r="D52" s="13"/>
-      <c r="E52" s="13"/>
-      <c r="F52" s="13"/>
-      <c r="G52" s="13"/>
-      <c r="H52" s="13"/>
-      <c r="I52" s="13"/>
-      <c r="J52" s="4"/>
-      <c r="K52" s="4"/>
-      <c r="L52" s="3"/>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A53" s="13"/>
       <c r="B53" s="13"/>
       <c r="C53" s="13"/>
       <c r="D53" s="13"/>
@@ -2528,34 +2552,37 @@
       <c r="L53" s="3"/>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A54" s="9"/>
-      <c r="B54" s="9"/>
-      <c r="C54" s="9"/>
-      <c r="D54" s="9"/>
-      <c r="E54" s="9"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="9"/>
-      <c r="H54" s="9"/>
-      <c r="I54" s="9"/>
+      <c r="A54" s="13"/>
+      <c r="B54" s="13"/>
+      <c r="C54" s="13"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
       <c r="J54" s="4"/>
       <c r="K54" s="4"/>
       <c r="L54" s="3"/>
     </row>
-    <row r="55" spans="1:12" s="5" customFormat="1" ht="12.5" x14ac:dyDescent="0.35">
-      <c r="A55" s="16" t="s">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A55" s="9"/>
+      <c r="B55" s="9"/>
+      <c r="C55" s="9"/>
+      <c r="D55" s="9"/>
+      <c r="E55" s="9"/>
+      <c r="F55" s="9"/>
+      <c r="G55" s="9"/>
+      <c r="H55" s="9"/>
+      <c r="I55" s="9"/>
+      <c r="J55" s="4"/>
+      <c r="K55" s="4"/>
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="1:12" s="5" customFormat="1" ht="12.5" x14ac:dyDescent="0.35">
+      <c r="A56" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B55" s="16"/>
-      <c r="C55" s="16"/>
-      <c r="D55" s="16"/>
-      <c r="E55" s="16"/>
-      <c r="F55" s="16"/>
-      <c r="G55" s="16"/>
-      <c r="H55" s="16"/>
-      <c r="I55" s="16"/>
-    </row>
-    <row r="56" spans="1:9" s="5" customFormat="1" ht="12.5" x14ac:dyDescent="0.35">
-      <c r="A56" s="16"/>
       <c r="B56" s="16"/>
       <c r="C56" s="16"/>
       <c r="D56" s="16"/>
@@ -2906,7 +2933,7 @@
       <c r="H87" s="16"/>
       <c r="I87" s="16"/>
     </row>
-    <row r="88" spans="1:9" s="5" customFormat="1" ht="13.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:9" s="5" customFormat="1" ht="12.5" x14ac:dyDescent="0.35">
       <c r="A88" s="16"/>
       <c r="B88" s="16"/>
       <c r="C88" s="16"/>
@@ -3104,7 +3131,7 @@
       <c r="H105" s="16"/>
       <c r="I105" s="16"/>
     </row>
-    <row r="106" spans="1:9" s="5" customFormat="1" ht="38.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:9" s="5" customFormat="1" ht="13.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="16"/>
       <c r="B106" s="16"/>
       <c r="C106" s="16"/>
@@ -3115,7 +3142,7 @@
       <c r="H106" s="16"/>
       <c r="I106" s="16"/>
     </row>
-    <row r="107" spans="1:9" s="5" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:9" s="5" customFormat="1" ht="38.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="16"/>
       <c r="B107" s="16"/>
       <c r="C107" s="16"/>
@@ -3126,7 +3153,7 @@
       <c r="H107" s="16"/>
       <c r="I107" s="16"/>
     </row>
-    <row r="108" spans="1:9" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:9" s="5" customFormat="1" ht="56.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="16"/>
       <c r="B108" s="16"/>
       <c r="C108" s="16"/>
@@ -3137,7 +3164,7 @@
       <c r="H108" s="16"/>
       <c r="I108" s="16"/>
     </row>
-    <row r="109" spans="1:9" s="5" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:9" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="16"/>
       <c r="B109" s="16"/>
       <c r="C109" s="16"/>
@@ -3148,7 +3175,7 @@
       <c r="H109" s="16"/>
       <c r="I109" s="16"/>
     </row>
-    <row r="110" spans="1:9" s="5" customFormat="1" ht="35.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:9" s="5" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="16"/>
       <c r="B110" s="16"/>
       <c r="C110" s="16"/>
@@ -3159,7 +3186,7 @@
       <c r="H110" s="16"/>
       <c r="I110" s="16"/>
     </row>
-    <row r="111" spans="1:9" s="5" customFormat="1" ht="53.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:9" s="5" customFormat="1" ht="35.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="16"/>
       <c r="B111" s="16"/>
       <c r="C111" s="16"/>
@@ -3170,7 +3197,7 @@
       <c r="H111" s="16"/>
       <c r="I111" s="16"/>
     </row>
-    <row r="112" spans="1:9" s="5" customFormat="1" ht="101.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:9" s="5" customFormat="1" ht="53.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="16"/>
       <c r="B112" s="16"/>
       <c r="C112" s="16"/>
@@ -3181,32 +3208,32 @@
       <c r="H112" s="16"/>
       <c r="I112" s="16"/>
     </row>
-    <row r="113" spans="1:9" s="5" customFormat="1" ht="13.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A113" s="8"/>
-      <c r="B113" s="8"/>
-      <c r="C113" s="8"/>
-      <c r="D113" s="8"/>
-      <c r="E113" s="8"/>
-      <c r="F113" s="8"/>
-      <c r="G113" s="8"/>
-      <c r="H113" s="8"/>
-      <c r="I113" s="8"/>
-    </row>
-    <row r="114" spans="1:9" s="5" customFormat="1" ht="13.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A114" s="17" t="s">
+    <row r="113" spans="1:9" s="5" customFormat="1" ht="101.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A113" s="16"/>
+      <c r="B113" s="16"/>
+      <c r="C113" s="16"/>
+      <c r="D113" s="16"/>
+      <c r="E113" s="16"/>
+      <c r="F113" s="16"/>
+      <c r="G113" s="16"/>
+      <c r="H113" s="16"/>
+      <c r="I113" s="16"/>
+    </row>
+    <row r="114" spans="1:9" s="5" customFormat="1" ht="13.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A114" s="8"/>
+      <c r="B114" s="8"/>
+      <c r="C114" s="8"/>
+      <c r="D114" s="8"/>
+      <c r="E114" s="8"/>
+      <c r="F114" s="8"/>
+      <c r="G114" s="8"/>
+      <c r="H114" s="8"/>
+      <c r="I114" s="8"/>
+    </row>
+    <row r="115" spans="1:9" s="5" customFormat="1" ht="13.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A115" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="B114" s="17"/>
-      <c r="C114" s="17"/>
-      <c r="D114" s="17"/>
-      <c r="E114" s="17"/>
-      <c r="F114" s="17"/>
-      <c r="G114" s="17"/>
-      <c r="H114" s="17"/>
-      <c r="I114" s="17"/>
-    </row>
-    <row r="115" spans="1:9" s="5" customFormat="1" ht="12.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A115" s="17"/>
       <c r="B115" s="17"/>
       <c r="C115" s="17"/>
       <c r="D115" s="17"/>
@@ -3260,7 +3287,7 @@
       <c r="H119" s="17"/>
       <c r="I119" s="17"/>
     </row>
-    <row r="120" spans="1:11" s="5" customFormat="1" ht="12.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:9" s="5" customFormat="1" ht="12.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="17"/>
       <c r="B120" s="17"/>
       <c r="C120" s="17"/>
@@ -3271,34 +3298,32 @@
       <c r="H120" s="17"/>
       <c r="I120" s="17"/>
     </row>
-    <row r="121" spans="1:11" s="5" customFormat="1" ht="13" x14ac:dyDescent="0.35">
-      <c r="A121" s="11"/>
-      <c r="B121" s="8"/>
-      <c r="C121" s="8"/>
-      <c r="D121" s="8"/>
-      <c r="E121" s="8"/>
-      <c r="F121" s="8"/>
-      <c r="G121" s="8"/>
-      <c r="H121" s="8"/>
-      <c r="I121" s="8"/>
-    </row>
-    <row r="122" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A122" s="16" t="s">
+    <row r="121" spans="1:11" s="5" customFormat="1" ht="12.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A121" s="17"/>
+      <c r="B121" s="17"/>
+      <c r="C121" s="17"/>
+      <c r="D121" s="17"/>
+      <c r="E121" s="17"/>
+      <c r="F121" s="17"/>
+      <c r="G121" s="17"/>
+      <c r="H121" s="17"/>
+      <c r="I121" s="17"/>
+    </row>
+    <row r="122" spans="1:11" s="5" customFormat="1" ht="13" x14ac:dyDescent="0.35">
+      <c r="A122" s="11"/>
+      <c r="B122" s="8"/>
+      <c r="C122" s="8"/>
+      <c r="D122" s="8"/>
+      <c r="E122" s="8"/>
+      <c r="F122" s="8"/>
+      <c r="G122" s="8"/>
+      <c r="H122" s="8"/>
+      <c r="I122" s="8"/>
+    </row>
+    <row r="123" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A123" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="B122" s="16"/>
-      <c r="C122" s="16"/>
-      <c r="D122" s="16"/>
-      <c r="E122" s="16"/>
-      <c r="F122" s="16"/>
-      <c r="G122" s="16"/>
-      <c r="H122" s="16"/>
-      <c r="I122" s="16"/>
-      <c r="J122" s="2"/>
-      <c r="K122" s="2"/>
-    </row>
-    <row r="123" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A123" s="16"/>
       <c r="B123" s="16"/>
       <c r="C123" s="16"/>
       <c r="D123" s="16"/>
@@ -3310,7 +3335,7 @@
       <c r="J123" s="2"/>
       <c r="K123" s="2"/>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="16"/>
       <c r="B124" s="16"/>
       <c r="C124" s="16"/>
@@ -3336,7 +3361,7 @@
       <c r="J125" s="2"/>
       <c r="K125" s="2"/>
     </row>
-    <row r="126" spans="1:11" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A126" s="16"/>
       <c r="B126" s="16"/>
       <c r="C126" s="16"/>
@@ -3349,7 +3374,7 @@
       <c r="J126" s="2"/>
       <c r="K126" s="2"/>
     </row>
-    <row r="127" spans="1:11" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:11" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="16"/>
       <c r="B127" s="16"/>
       <c r="C127" s="16"/>
@@ -3362,7 +3387,7 @@
       <c r="J127" s="2"/>
       <c r="K127" s="2"/>
     </row>
-    <row r="128" spans="1:11" ht="3" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:11" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="16"/>
       <c r="B128" s="16"/>
       <c r="C128" s="16"/>
@@ -3375,7 +3400,7 @@
       <c r="J128" s="2"/>
       <c r="K128" s="2"/>
     </row>
-    <row r="129" spans="1:11" ht="8.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:11" ht="3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="16"/>
       <c r="B129" s="16"/>
       <c r="C129" s="16"/>
@@ -3388,36 +3413,36 @@
       <c r="J129" s="2"/>
       <c r="K129" s="2"/>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A130" s="6"/>
-      <c r="B130" s="7"/>
-      <c r="C130" s="7"/>
-      <c r="D130" s="7"/>
-      <c r="E130" s="7"/>
-      <c r="F130" s="7"/>
-      <c r="G130" s="7"/>
-      <c r="H130" s="7"/>
-      <c r="I130" s="7"/>
+    <row r="130" spans="1:11" ht="8.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A130" s="16"/>
+      <c r="B130" s="16"/>
+      <c r="C130" s="16"/>
+      <c r="D130" s="16"/>
+      <c r="E130" s="16"/>
+      <c r="F130" s="16"/>
+      <c r="G130" s="16"/>
+      <c r="H130" s="16"/>
+      <c r="I130" s="16"/>
       <c r="J130" s="2"/>
       <c r="K130" s="2"/>
     </row>
-    <row r="131" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A131" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="B131" s="15"/>
-      <c r="C131" s="15"/>
-      <c r="D131" s="15"/>
-      <c r="E131" s="15"/>
-      <c r="F131" s="15"/>
-      <c r="G131" s="15"/>
-      <c r="H131" s="15"/>
-      <c r="I131" s="15"/>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A131" s="6"/>
+      <c r="B131" s="7"/>
+      <c r="C131" s="7"/>
+      <c r="D131" s="7"/>
+      <c r="E131" s="7"/>
+      <c r="F131" s="7"/>
+      <c r="G131" s="7"/>
+      <c r="H131" s="7"/>
+      <c r="I131" s="7"/>
       <c r="J131" s="2"/>
       <c r="K131" s="2"/>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A132" s="15"/>
+    <row r="132" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A132" s="15" t="s">
+        <v>9</v>
+      </c>
       <c r="B132" s="15"/>
       <c r="C132" s="15"/>
       <c r="D132" s="15"/>
@@ -3426,6 +3451,8 @@
       <c r="G132" s="15"/>
       <c r="H132" s="15"/>
       <c r="I132" s="15"/>
+      <c r="J132" s="2"/>
+      <c r="K132" s="2"/>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A133" s="15"/>
@@ -3460,7 +3487,7 @@
       <c r="H135" s="15"/>
       <c r="I135" s="15"/>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A136" s="15"/>
       <c r="B136" s="15"/>
       <c r="C136" s="15"/>
@@ -3526,18 +3553,29 @@
       <c r="H141" s="15"/>
       <c r="I141" s="15"/>
     </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A142" s="15"/>
+      <c r="B142" s="15"/>
+      <c r="C142" s="15"/>
+      <c r="D142" s="15"/>
+      <c r="E142" s="15"/>
+      <c r="F142" s="15"/>
+      <c r="G142" s="15"/>
+      <c r="H142" s="15"/>
+      <c r="I142" s="15"/>
+    </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A46:I46"/>
-    <mergeCell ref="A52:I53"/>
-    <mergeCell ref="A48:I50"/>
-    <mergeCell ref="A131:I141"/>
-    <mergeCell ref="A55:I112"/>
-    <mergeCell ref="A114:I120"/>
-    <mergeCell ref="A122:I129"/>
+    <mergeCell ref="A47:I47"/>
+    <mergeCell ref="A53:I54"/>
+    <mergeCell ref="A49:I51"/>
+    <mergeCell ref="A132:I142"/>
+    <mergeCell ref="A56:I113"/>
+    <mergeCell ref="A115:I121"/>
+    <mergeCell ref="A123:I130"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A46" r:id="rId1" xr:uid="{AADE94C5-E727-46BF-BFEF-E0B2BBB2518C}"/>
+    <hyperlink ref="A47" r:id="rId1" xr:uid="{AADE94C5-E727-46BF-BFEF-E0B2BBB2518C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
